--- a/data/preprocessed/street_sign_class_mapping.xlsx
+++ b/data/preprocessed/street_sign_class_mapping.xlsx
@@ -16,6 +16,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">canonical_mapping!$A$1:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">italy_classes!$A$1:$F$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">germany_classes!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">README!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">canonical_mapping!$A$1:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">italy_classes!$A$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">germany_classes!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>Purpose</t>
   </si>
@@ -397,9 +401,6 @@
   </si>
   <si>
     <t>warn_wild_animals</t>
-  </si>
-  <si>
-    <t>37?</t>
   </si>
   <si>
     <t>wild_animals_crossing</t>
@@ -2301,17 +2302,17 @@
       <c r="D53" t="s">
         <v>123</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="2">
+        <v>37</v>
+      </c>
+      <c r="F53" t="s">
         <v>124</v>
-      </c>
-      <c r="F53" t="s">
-        <v>125</v>
       </c>
       <c r="G53" t="s">
         <v>33</v>
       </c>
       <c r="H53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54">
@@ -2319,13 +2320,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C54">
         <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G54" t="s">
         <v>33</v>
@@ -2336,19 +2337,19 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C55">
         <v>53</v>
       </c>
       <c r="D55" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" t="s">
         <v>128</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>129</v>
-      </c>
-      <c r="F55" t="s">
-        <v>130</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -2362,13 +2363,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C56">
         <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G56" t="s">
         <v>33</v>
@@ -2379,19 +2380,19 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57">
         <v>55</v>
       </c>
       <c r="D57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" t="s">
         <v>132</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>133</v>
-      </c>
-      <c r="F57" t="s">
-        <v>134</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -2405,19 +2406,19 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58">
         <v>56</v>
       </c>
       <c r="D58" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" t="s">
         <v>135</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>136</v>
-      </c>
-      <c r="F58" t="s">
-        <v>137</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -2431,25 +2432,25 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C59">
         <v>57</v>
       </c>
       <c r="D59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E59" s="2">
         <v>31</v>
       </c>
       <c r="F59" t="s">
+        <v>138</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
         <v>139</v>
-      </c>
-      <c r="G59" t="s">
-        <v>25</v>
-      </c>
-      <c r="H59" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="60">
@@ -2457,19 +2458,19 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60">
         <v>58</v>
       </c>
       <c r="D60" t="s">
+        <v>140</v>
+      </c>
+      <c r="E60" t="s">
         <v>141</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>142</v>
-      </c>
-      <c r="F60" t="s">
-        <v>143</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
@@ -2483,19 +2484,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61">
         <v>59</v>
       </c>
       <c r="D61" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" t="s">
         <v>144</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>145</v>
-      </c>
-      <c r="F61" t="s">
-        <v>146</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
@@ -2509,13 +2510,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C62">
         <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G62" t="s">
         <v>33</v>
@@ -2526,19 +2527,19 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C63">
         <v>61</v>
       </c>
       <c r="D63" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" t="s">
         <v>148</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>149</v>
-      </c>
-      <c r="F63" t="s">
-        <v>150</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -2552,19 +2553,19 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C64">
         <v>62</v>
       </c>
       <c r="D64" t="s">
+        <v>150</v>
+      </c>
+      <c r="E64" t="s">
         <v>151</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>152</v>
-      </c>
-      <c r="F64" t="s">
-        <v>153</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
@@ -2578,13 +2579,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E65" s="2">
         <v>6</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
@@ -2598,13 +2599,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
@@ -2618,13 +2619,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
-      </c>
-      <c r="E67">
+        <v>156</v>
+      </c>
+      <c r="E67" s="2">
         <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -2644,7 +2645,7 @@
         <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -2658,13 +2659,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E69" s="2">
         <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -2678,13 +2679,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E70" s="2">
         <v>24</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -2698,13 +2699,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E71" s="2">
         <v>30</v>
       </c>
       <c r="F71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -2718,13 +2719,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72" s="2">
+        <v>32</v>
+      </c>
+      <c r="F72" t="s">
         <v>162</v>
-      </c>
-      <c r="E72">
-        <v>32</v>
-      </c>
-      <c r="F72" t="s">
-        <v>163</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -2738,13 +2739,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73" s="2">
+        <v>41</v>
+      </c>
+      <c r="F73" t="s">
         <v>164</v>
-      </c>
-      <c r="E73">
-        <v>41</v>
-      </c>
-      <c r="F73" t="s">
-        <v>165</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -2758,13 +2759,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
+        <v>165</v>
+      </c>
+      <c r="E74" s="2">
+        <v>42</v>
+      </c>
+      <c r="F74" t="s">
         <v>166</v>
-      </c>
-      <c r="E74">
-        <v>42</v>
-      </c>
-      <c r="F74" t="s">
-        <v>167</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -2797,16 +2798,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -3230,7 +3231,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
@@ -3238,7 +3239,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56">
@@ -3246,7 +3247,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57">
@@ -3254,7 +3255,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58">
@@ -3262,7 +3263,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59">
@@ -3270,7 +3271,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60">
@@ -3278,7 +3279,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61">
@@ -3286,7 +3287,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62">
@@ -3294,7 +3295,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63">
@@ -3302,7 +3303,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64">
@@ -3310,7 +3311,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3337,13 +3338,13 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -3363,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" t="s">
         <v>175</v>
-      </c>
-      <c r="F2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="3">
@@ -3383,10 +3384,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" t="s">
         <v>175</v>
-      </c>
-      <c r="F3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="4">
@@ -3403,10 +3404,10 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" t="s">
         <v>175</v>
-      </c>
-      <c r="F4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -3423,10 +3424,10 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" t="s">
         <v>175</v>
-      </c>
-      <c r="F5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="6">
@@ -3443,10 +3444,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" t="s">
         <v>175</v>
-      </c>
-      <c r="F6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -3463,10 +3464,10 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" t="s">
         <v>175</v>
-      </c>
-      <c r="F7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -3474,10 +3475,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" t="s">
         <v>177</v>
-      </c>
-      <c r="E8" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="9">
@@ -3494,10 +3495,10 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" t="s">
         <v>175</v>
-      </c>
-      <c r="F9" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -3514,10 +3515,10 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" t="s">
         <v>175</v>
-      </c>
-      <c r="F10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3534,10 +3535,10 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" t="s">
         <v>175</v>
-      </c>
-      <c r="F11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -3554,10 +3555,10 @@
         <v>21</v>
       </c>
       <c r="E12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" t="s">
         <v>175</v>
-      </c>
-      <c r="F12" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -3565,10 +3566,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
@@ -3585,10 +3586,10 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" t="s">
         <v>175</v>
-      </c>
-      <c r="F14" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="15">
@@ -3605,10 +3606,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" t="s">
         <v>175</v>
-      </c>
-      <c r="F15" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="16">
@@ -3625,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" t="s">
         <v>175</v>
-      </c>
-      <c r="F16" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="17">
@@ -3636,10 +3637,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18">
@@ -3656,10 +3657,10 @@
         <v>25</v>
       </c>
       <c r="E18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" t="s">
         <v>175</v>
-      </c>
-      <c r="F18" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19">
@@ -3676,10 +3677,10 @@
         <v>17</v>
       </c>
       <c r="E19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" t="s">
         <v>175</v>
-      </c>
-      <c r="F19" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="20">
@@ -3687,10 +3688,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21">
@@ -3707,10 +3708,10 @@
         <v>38</v>
       </c>
       <c r="E21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F21" t="s">
         <v>175</v>
-      </c>
-      <c r="F21" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="22">
@@ -3727,10 +3728,10 @@
         <v>39</v>
       </c>
       <c r="E22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" t="s">
         <v>175</v>
-      </c>
-      <c r="F22" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="23">
@@ -3738,10 +3739,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
@@ -3749,10 +3750,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25">
@@ -3769,10 +3770,10 @@
         <v>46</v>
       </c>
       <c r="E25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" t="s">
         <v>175</v>
-      </c>
-      <c r="F25" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="26">
@@ -3780,10 +3781,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27">
@@ -3800,10 +3801,10 @@
         <v>35</v>
       </c>
       <c r="E27" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" t="s">
         <v>175</v>
-      </c>
-      <c r="F27" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28">
@@ -3820,10 +3821,10 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" t="s">
         <v>175</v>
-      </c>
-      <c r="F28" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="29">
@@ -3840,10 +3841,10 @@
         <v>36</v>
       </c>
       <c r="E29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" t="s">
         <v>175</v>
-      </c>
-      <c r="F29" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="30">
@@ -3860,10 +3861,10 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
         <v>175</v>
-      </c>
-      <c r="F30" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="31">
@@ -3880,10 +3881,10 @@
         <v>37</v>
       </c>
       <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" t="s">
         <v>175</v>
-      </c>
-      <c r="F31" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="32">
@@ -3891,10 +3892,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
@@ -3902,7 +3903,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
         <v>123</v>
@@ -3911,10 +3912,10 @@
         <v>51</v>
       </c>
       <c r="E33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33" t="s">
         <v>175</v>
-      </c>
-      <c r="F33" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="34">
@@ -3922,10 +3923,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35">
@@ -3933,19 +3934,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35">
         <v>55</v>
       </c>
       <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
         <v>175</v>
-      </c>
-      <c r="F35" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="36">
@@ -3953,19 +3954,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36">
         <v>53</v>
       </c>
       <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" t="s">
         <v>175</v>
-      </c>
-      <c r="F36" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="37">
@@ -3973,19 +3974,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D37">
         <v>56</v>
       </c>
       <c r="E37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" t="s">
         <v>175</v>
-      </c>
-      <c r="F37" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="38">
@@ -3993,19 +3994,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38">
         <v>58</v>
       </c>
       <c r="E38" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" t="s">
         <v>175</v>
-      </c>
-      <c r="F38" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="39">
@@ -4013,19 +4014,19 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D39">
         <v>57</v>
       </c>
       <c r="E39" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" t="s">
         <v>175</v>
-      </c>
-      <c r="F39" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="40">
@@ -4033,19 +4034,19 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D40">
         <v>61</v>
       </c>
       <c r="E40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" t="s">
         <v>175</v>
-      </c>
-      <c r="F40" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="41">
@@ -4053,19 +4054,19 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D41">
         <v>59</v>
       </c>
       <c r="E41" t="s">
+        <v>174</v>
+      </c>
+      <c r="F41" t="s">
         <v>175</v>
-      </c>
-      <c r="F41" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="42">
@@ -4073,19 +4074,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D42">
         <v>62</v>
       </c>
       <c r="E42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F42" t="s">
         <v>175</v>
-      </c>
-      <c r="F42" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="43">
@@ -4093,10 +4094,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44">
@@ -4104,10 +4105,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45">
@@ -4115,13 +4116,13 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
         <v>189</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>190</v>
-      </c>
-      <c r="F45" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
